--- a/Daysight Manual Amazon Inputs - XLS Format_v2.0.xlsx
+++ b/Daysight Manual Amazon Inputs - XLS Format_v2.0.xlsx
@@ -680,7 +680,6 @@
           <t>Insulated and leak-proof with a built-in straw. Fits any cup holder.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -770,7 +769,6 @@
           <t>Instant-read digital thermometer, perfect for grilling and roasting.</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -858,7 +856,6 @@
           <t>The inside story of one of tech's most ambitious and polarizing people.</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -948,7 +945,6 @@
           <t>A true story of greed and insider trading on Wall Street.</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1038,7 +1034,6 @@
           <t>Active noise cancelling, all-day comfort, and seamless Apple pairing.</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1222,7 +1217,6 @@
           <t>Five colorful squeaky plush toys in different shapes and sizes.</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1261,7 +1255,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,7 +1349,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1500,7 +1494,6 @@
           <t>Official US Open ball, sold in a 3-pack. Great for regular players.</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1590,7 +1583,6 @@
           <t>Ceremonial grade matcha powder that blends smooth into lattes and tea.</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1680,7 +1672,6 @@
           <t>Tiny Bluetooth tracker for keys, bags, or anything you tend to lose.</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1768,7 +1759,6 @@
           <t>How Uber and Airbnb rewrote the rules of business from the ground up.</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1856,7 +1846,6 @@
           <t>The story behind Jeff Bezos, Amazon, and building a retail empire.</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1946,7 +1935,6 @@
           <t>The classic quest that launched Middle-earth. A beloved adventure for all ages.</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2034,7 +2022,6 @@
           <t>The first book in the Lord of the Rings trilogy. Essential fantasy fiction.</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2122,7 +2109,6 @@
           <t>A practical guide to building good habits and breaking bad ones.</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2161,7 +2147,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2212,7 +2198,6 @@
           <t>Lightweight, cushioned, and easy to clean. Fits a wide range of occasions.</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2302,7 +2287,6 @@
           <t>Cushioned cotton crew socks in a 6-pack. A reliable everyday staple.</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2392,7 +2376,6 @@
           <t>Comes with two paddles, three balls, and a handy carrying case.</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2482,7 +2465,6 @@
           <t>A colorful buildable plant set that looks great on any desk or shelf.</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2521,7 +2503,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2572,7 +2554,6 @@
           <t>Roses, carnations, and veronica arranged in soft pastel tones.</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2611,7 +2592,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2662,7 +2643,6 @@
           <t>A bold arrangement of roses, thistle, and craspedia in warm tones.</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2752,7 +2732,6 @@
           <t>Lush pink peonies with seasonal greenery. A crowd-pleasing classic.</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2842,7 +2821,6 @@
           <t>A premium assortment of Rocher, Rondnoir, and Raffaello chocolates.</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2932,7 +2910,6 @@
           <t>Dubai-style chocolate bar with pistachio and knafeh filling inside.</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3022,7 +2999,6 @@
           <t>The original 3x3 puzzle cube. Still tricky, still fun.</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3112,7 +3088,6 @@
           <t>Keeps drinks cold for hours and fits in a car cup holder. Flip straw.</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3202,7 +3177,6 @@
           <t>Crisp and elegant French champagne, sold as a convenient half bottle.</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3292,7 +3266,6 @@
           <t>A well-rounded Bordeaux red with dark fruit and a smooth finish.</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3331,7 +3304,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3382,7 +3355,6 @@
           <t>Bright California chardonnay with balanced citrus and a touch of oak.</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3472,7 +3444,6 @@
           <t>Clean protein bar made with egg whites, dates, and nuts. No fillers.</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3562,7 +3533,6 @@
           <t>60 individually wrapped milk chocolate truffles in a shareable gift box.</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3652,7 +3622,6 @@
           <t>Long-lasting reed diffuser that fills a room without needing a flame.</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3742,7 +3711,6 @@
           <t>Insulated stainless steel tumbler that keeps coffee hot for hours.</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3926,7 +3894,6 @@
           <t>Simple and accurate digital kitchen scale for cooking, baking, and prep.</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4016,7 +3983,6 @@
           <t>15W wireless charging pad that works with any Qi-compatible phone.</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4106,7 +4072,6 @@
           <t>Fitness tracking, heart rate monitoring, and notifications on your wrist.</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4145,7 +4110,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4196,7 +4161,6 @@
           <t>Lightweight wireless headphones with a 50-hour battery and clear sound.</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4235,7 +4199,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4474,7 +4438,6 @@
           <t>High-strength vitamin D3 capsules intended to support immune function and bone health.</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4564,7 +4527,6 @@
           <t>Fizzy vitamin C drink packets with zinc and electrolytes. 30 servings.</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4654,7 +4616,6 @@
           <t>Gentle magnesium supplement designed to support sleep, relaxation, and muscle recovery.</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4744,7 +4705,6 @@
           <t>The classic Adidas Samba in black and white. A staple sneaker.</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4783,7 +4743,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4877,7 +4837,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -4928,7 +4888,6 @@
           <t>Mushroom-based coffee alternative with mushroom extract and less caffeine.</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5018,7 +4977,6 @@
           <t>Classic Italian espresso grind, smooth medium roast with balanced flavor.</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5108,7 +5066,6 @@
           <t>Reusable lint roller that lifts pet hair from furniture and car seats.</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5241,7 +5198,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -5335,7 +5292,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -5480,7 +5437,6 @@
           <t>The classic pull-a-block tower game. Simple rules, fun with groups.</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5570,7 +5526,6 @@
           <t>Oversized UNO cards that make game night louder and harder to ignore.</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5660,7 +5615,6 @@
           <t>A rich and structured Napa cabernet from the Stags Leap district.</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5699,7 +5653,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -5750,7 +5704,6 @@
           <t>Light and earthy pinot noir from Los Carneros with soft berry notes.</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5838,7 +5791,6 @@
           <t>A grumpy widower finds unexpected friendships in this bestselling novel.</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5877,7 +5829,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -5928,7 +5880,6 @@
           <t>A warm and cheerful mix of orange roses, delphinium, and lisianthus.</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5967,7 +5918,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -6018,7 +5969,6 @@
           <t>Pink roses paired with hypericum berries and lush seasonal greenery.</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6057,7 +6007,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -6108,7 +6058,6 @@
           <t>A playful purple, pink, and white arrangement with roses and carnations.</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6198,7 +6147,6 @@
           <t>Portable Bluetooth speaker with full bass and 24-hour battery life.</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6288,7 +6236,6 @@
           <t>Premium on-ear headphones with spatial audio and up to 50 hours of play.</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6378,7 +6325,6 @@
           <t>Slim Bluetooth tracker that clips onto keys, slides into wallets or bags.</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6468,7 +6414,6 @@
           <t>Assorted incense sticks in a sampler box with classic and floral scents.</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6558,7 +6503,6 @@
           <t>High-fidelity ear plugs that reduce volume without muddying the sound.</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6597,7 +6541,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -6648,7 +6592,6 @@
           <t>Well-known Veuve Clicquot champagne. Dry, balanced, and full-bodied.</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
